--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/EstItens_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/EstItens_3EM_MT_S3.xlsx
@@ -50,6 +50,9 @@
     <t xml:space="preserve">004</t>
   </si>
   <si>
+    <t xml:space="preserve">Sim</t>
+  </si>
+  <si>
     <t xml:space="preserve">005</t>
   </si>
   <si>
@@ -57,9 +60,6 @@
   </si>
   <si>
     <t xml:space="preserve">008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sim</t>
   </si>
   <si>
     <t xml:space="preserve">009</t>
@@ -467,19 +467,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1.51105372980073</v>
+        <v>1.41041283551783</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5908626040372</v>
+        <v>2.56561247672914</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0302210745960145</v>
+        <v>0.0282082567103566</v>
       </c>
       <c r="E2" t="n">
-        <v>379.54313020186</v>
+        <v>378.280623836457</v>
       </c>
       <c r="F2" t="n">
-        <v>0.324006976163134</v>
+        <v>0.31913707968733</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -490,19 +490,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1.78569302564122</v>
+        <v>1.7178463902522</v>
       </c>
       <c r="C3" t="n">
-        <v>2.81745761809315</v>
+        <v>2.81915183616893</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0357138605128244</v>
+        <v>0.0343569278050439</v>
       </c>
       <c r="E3" t="n">
-        <v>390.872880904657</v>
+        <v>390.957591808447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.16380999647197</v>
+        <v>0.163906739545904</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -513,19 +513,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1.32820604861897</v>
+        <v>1.26213058974417</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5883958146468</v>
+        <v>2.5641008111472</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0265641209723795</v>
+        <v>0.0252426117948834</v>
       </c>
       <c r="E4" t="n">
-        <v>379.41979073234</v>
+        <v>378.20504055736</v>
       </c>
       <c r="F4" t="n">
-        <v>0.172010087431202</v>
+        <v>0.168021252815295</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -536,65 +536,65 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.326814983285238</v>
+        <v>0.182778430139589</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7231833803097</v>
+        <v>4.79930977775087</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00653629966570477</v>
+        <v>0.00365556860279178</v>
       </c>
       <c r="E5" t="n">
-        <v>386.159169015485</v>
+        <v>489.965488887544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0294104834032611</v>
+        <v>0.0459882824458234</v>
       </c>
       <c r="G5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1.39129353854177</v>
+        <v>2.26596614775883</v>
       </c>
       <c r="C6" t="n">
-        <v>2.17637250150481</v>
+        <v>2.19308960864848</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0278258707708354</v>
+        <v>0.0453193229551767</v>
       </c>
       <c r="E6" t="n">
-        <v>358.81862507524</v>
+        <v>359.654480432424</v>
       </c>
       <c r="F6" t="n">
-        <v>0.138709531457977</v>
+        <v>0.239138866944971</v>
       </c>
       <c r="G6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.82626529620734</v>
+        <v>2.7460179458303</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7211506276216</v>
+        <v>2.72045927618192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0565253059241469</v>
+        <v>0.054920358916606</v>
       </c>
       <c r="E7" t="n">
-        <v>386.05753138108</v>
+        <v>386.022963809096</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0889827852951722</v>
+        <v>0.0893318548406571</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -602,16 +602,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" t="n">
         <v>2.8</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3391</v>
+        <v>3.33909999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.056</v>
+        <v>0.0560000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>416.955</v>
@@ -620,7 +620,7 @@
         <v>0.197</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -628,13 +628,13 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.24083909397092</v>
+        <v>4.24083909397093</v>
       </c>
       <c r="C9" t="n">
         <v>2.47757258673408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0848167818794185</v>
+        <v>0.0848167818794186</v>
       </c>
       <c r="E9" t="n">
         <v>373.878629336704</v>
@@ -643,7 +643,7 @@
         <v>0.225826940012559</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -651,19 +651,19 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1.43889895453277</v>
+        <v>1.32433141789366</v>
       </c>
       <c r="C10" t="n">
-        <v>2.1052584703685</v>
+        <v>2.04150159751268</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0287779790906554</v>
+        <v>0.0264866283578733</v>
       </c>
       <c r="E10" t="n">
-        <v>355.262923518425</v>
+        <v>352.075079875634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.141887712705839</v>
+        <v>0.129833047075147</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
@@ -674,7 +674,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.89999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="C11" t="n">
         <v>2.57</v>
@@ -689,7 +689,7 @@
         <v>0.087</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -697,19 +697,19 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.26112094667919</v>
+        <v>1.20212653371931</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9989377871876</v>
+        <v>1.95536470145416</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0252224189335837</v>
+        <v>0.0240425306743863</v>
       </c>
       <c r="E12" t="n">
-        <v>349.94688935938</v>
+        <v>347.768235072708</v>
       </c>
       <c r="F12" t="n">
-        <v>0.207645601624839</v>
+        <v>0.205163025765816</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
@@ -732,10 +732,10 @@
         <v>376.164</v>
       </c>
       <c r="F13" t="n">
-        <v>0.166000000000001</v>
+        <v>0.166</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
@@ -743,22 +743,22 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>2.32332512508159</v>
+        <v>1.65</v>
       </c>
       <c r="C14" t="n">
-        <v>2.18654773098345</v>
+        <v>2.83643999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0464665025016318</v>
+        <v>0.0330000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>359.327386549173</v>
+        <v>391.822</v>
       </c>
       <c r="F14" t="n">
-        <v>0.114440582379926</v>
+        <v>0.22</v>
       </c>
       <c r="G14" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -766,7 +766,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>0.999586439155039</v>
+        <v>0.999586439155041</v>
       </c>
       <c r="C15" t="n">
         <v>1.46403515763454</v>
@@ -778,10 +778,10 @@
         <v>323.201757881727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0384352417367561</v>
+        <v>0.0384352417367562</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +789,7 @@
         <v>23</v>
       </c>
       <c r="B16" t="n">
-        <v>1.95898986275128</v>
+        <v>1.95898986275129</v>
       </c>
       <c r="C16" t="n">
         <v>2.71575227825572</v>
@@ -804,7 +804,7 @@
         <v>0.171681190023679</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
@@ -812,19 +812,19 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>1.17480743735632</v>
+        <v>1.11711841032481</v>
       </c>
       <c r="C17" t="n">
-        <v>3.53163739630619</v>
+        <v>3.56612025839991</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0234961487471264</v>
+        <v>0.0223423682064962</v>
       </c>
       <c r="E17" t="n">
-        <v>426.581869815309</v>
+        <v>428.306012919996</v>
       </c>
       <c r="F17" t="n">
-        <v>0.130360180806821</v>
+        <v>0.129465101251646</v>
       </c>
       <c r="G17" t="s">
         <v>8</v>
@@ -835,19 +835,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.9236076195866</v>
+        <v>1.79486274477217</v>
       </c>
       <c r="C18" t="n">
-        <v>2.52321877959688</v>
+        <v>2.50432788985657</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0384721523917321</v>
+        <v>0.0358972548954433</v>
       </c>
       <c r="E18" t="n">
-        <v>376.160938979844</v>
+        <v>375.216394492828</v>
       </c>
       <c r="F18" t="n">
-        <v>0.132925678579582</v>
+        <v>0.129023284057307</v>
       </c>
       <c r="G18" t="s">
         <v>8</v>
@@ -858,19 +858,19 @@
         <v>26</v>
       </c>
       <c r="B19" t="n">
-        <v>1.96005471513591</v>
+        <v>1.88073317781561</v>
       </c>
       <c r="C19" t="n">
-        <v>3.10520827122798</v>
+        <v>3.12509482514695</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0392010943027182</v>
+        <v>0.0376146635563123</v>
       </c>
       <c r="E19" t="n">
-        <v>405.260413561399</v>
+        <v>406.254741257348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.168814133362762</v>
+        <v>0.169442444004338</v>
       </c>
       <c r="G19" t="s">
         <v>8</v>
@@ -881,22 +881,22 @@
         <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>0.397234664245573</v>
+        <v>0.315058689447332</v>
       </c>
       <c r="C20" t="n">
-        <v>3.31214502219521</v>
+        <v>4.4330977883949</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00794469328491146</v>
+        <v>0.00630117378894664</v>
       </c>
       <c r="E20" t="n">
-        <v>415.60725110976</v>
+        <v>471.654889419745</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0453402976583313</v>
+        <v>0.0633161106344133</v>
       </c>
       <c r="G20" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -904,22 +904,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>1.01748132037659</v>
+        <v>1.22539680568554</v>
       </c>
       <c r="C21" t="n">
-        <v>4.23209713024349</v>
+        <v>3.80487272141349</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0203496264075317</v>
+        <v>0.0245079361137108</v>
       </c>
       <c r="E21" t="n">
-        <v>461.604856512175</v>
+        <v>440.243636070675</v>
       </c>
       <c r="F21" t="n">
-        <v>0.123710225037743</v>
+        <v>0.167865500389049</v>
       </c>
       <c r="G21" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -927,22 +927,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.46832046316697</v>
+        <v>1.25059970266019</v>
       </c>
       <c r="C22" t="n">
-        <v>3.0976020240032</v>
+        <v>3.27043048951258</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0293664092633395</v>
+        <v>0.0250119940532037</v>
       </c>
       <c r="E22" t="n">
-        <v>404.88010120016</v>
+        <v>413.521524475629</v>
       </c>
       <c r="F22" t="n">
-        <v>0.164280867547475</v>
+        <v>0.210710742915288</v>
       </c>
       <c r="G22" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -965,7 +965,7 @@
         <v>0.171925820258486</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -988,7 +988,7 @@
         <v>0.158065373745723</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -996,13 +996,13 @@
         <v>32</v>
       </c>
       <c r="B25" t="n">
-        <v>2.7891462044451</v>
+        <v>2.78914620444511</v>
       </c>
       <c r="C25" t="n">
-        <v>2.33940076682625</v>
+        <v>2.33940076682624</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0557829240889021</v>
+        <v>0.0557829240889023</v>
       </c>
       <c r="E25" t="n">
         <v>366.970038341312</v>
@@ -1011,7 +1011,7 @@
         <v>0.167862052302509</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/EstItens_3EM_MT_S3.xlsx
+++ b/Piaui/2026/Julho/ResultadosTRI_3EM_MT/Simulado_III/EstItens_3EM_MT_S3.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">004</t>
   </si>
   <si>
+    <t xml:space="preserve">005</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">005</t>
   </si>
   <si>
     <t xml:space="preserve">007</t>
@@ -467,19 +467,19 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1.41041283551783</v>
+        <v>1.54750666371777</v>
       </c>
       <c r="C2" t="n">
-        <v>2.56561247672914</v>
+        <v>2.58057042301361</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0282082567103566</v>
+        <v>0.0309501332743554</v>
       </c>
       <c r="E2" t="n">
-        <v>378.280623836457</v>
+        <v>379.028521150681</v>
       </c>
       <c r="F2" t="n">
-        <v>0.31913707968733</v>
+        <v>0.327519718143027</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -490,19 +490,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1.7178463902522</v>
+        <v>1.82848167897348</v>
       </c>
       <c r="C3" t="n">
-        <v>2.81915183616893</v>
+        <v>2.80097283152975</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0343569278050439</v>
+        <v>0.0365696335794696</v>
       </c>
       <c r="E3" t="n">
-        <v>390.957591808447</v>
+        <v>390.048641576488</v>
       </c>
       <c r="F3" t="n">
-        <v>0.163906739545904</v>
+        <v>0.166370860269202</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -513,19 +513,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1.26213058974417</v>
+        <v>1.34233611570772</v>
       </c>
       <c r="C4" t="n">
-        <v>2.5641008111472</v>
+        <v>2.57079358317082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0252426117948834</v>
+        <v>0.0268467223141545</v>
       </c>
       <c r="E4" t="n">
-        <v>378.20504055736</v>
+        <v>378.539679158541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.168021252815295</v>
+        <v>0.173802471394774</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
@@ -536,27 +536,27 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.182778430139589</v>
+        <v>0.328485258251187</v>
       </c>
       <c r="C5" t="n">
-        <v>4.79930977775087</v>
+        <v>2.69639485725664</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00365556860279178</v>
+        <v>0.00656970516502374</v>
       </c>
       <c r="E5" t="n">
-        <v>489.965488887544</v>
+        <v>384.819742862832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0459882824458234</v>
+        <v>0.0297470500193034</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
         <v>2.26596614775883</v>
@@ -574,7 +574,7 @@
         <v>0.239138866944971</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -582,19 +582,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.7460179458303</v>
+        <v>2.86987553662492</v>
       </c>
       <c r="C7" t="n">
-        <v>2.72045927618192</v>
+        <v>2.70620763264154</v>
       </c>
       <c r="D7" t="n">
-        <v>0.054920358916606</v>
+        <v>0.0573975107324984</v>
       </c>
       <c r="E7" t="n">
-        <v>386.022963809096</v>
+        <v>385.310381632077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0893318548406571</v>
+        <v>0.0903638608271887</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -608,10 +608,10 @@
         <v>2.8</v>
       </c>
       <c r="C8" t="n">
-        <v>3.33909999999999</v>
+        <v>3.3391</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0560000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="E8" t="n">
         <v>416.955</v>
@@ -620,7 +620,7 @@
         <v>0.197</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -634,7 +634,7 @@
         <v>2.47757258673408</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0848167818794186</v>
+        <v>0.0848167818794185</v>
       </c>
       <c r="E9" t="n">
         <v>373.878629336704</v>
@@ -643,7 +643,7 @@
         <v>0.225826940012559</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -651,19 +651,19 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1.32433141789366</v>
+        <v>1.42835266501804</v>
       </c>
       <c r="C10" t="n">
-        <v>2.04150159751268</v>
+        <v>2.07887428001701</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0264866283578733</v>
+        <v>0.0285670533003607</v>
       </c>
       <c r="E10" t="n">
-        <v>352.075079875634</v>
+        <v>353.943714000851</v>
       </c>
       <c r="F10" t="n">
-        <v>0.129833047075147</v>
+        <v>0.139983841301423</v>
       </c>
       <c r="G10" t="s">
         <v>8</v>
@@ -674,7 +674,7 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.9</v>
+        <v>6.90000000000001</v>
       </c>
       <c r="C11" t="n">
         <v>2.57</v>
@@ -686,10 +686,10 @@
         <v>378.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.087</v>
+        <v>0.0869999999999999</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -697,19 +697,19 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.20212653371931</v>
+        <v>1.22360284377339</v>
       </c>
       <c r="C12" t="n">
-        <v>1.95536470145416</v>
+        <v>1.93913236113334</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0240425306743863</v>
+        <v>0.0244720568754678</v>
       </c>
       <c r="E12" t="n">
-        <v>347.768235072708</v>
+        <v>346.956618056667</v>
       </c>
       <c r="F12" t="n">
-        <v>0.205163025765816</v>
+        <v>0.195710397756119</v>
       </c>
       <c r="G12" t="s">
         <v>8</v>
@@ -735,7 +735,7 @@
         <v>0.166</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -743,22 +743,22 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>1.65</v>
+        <v>2.30774197789211</v>
       </c>
       <c r="C14" t="n">
-        <v>2.83643999999999</v>
+        <v>2.16537606957675</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0330000000000001</v>
+        <v>0.0461548395578422</v>
       </c>
       <c r="E14" t="n">
-        <v>391.822</v>
+        <v>358.268803478838</v>
       </c>
       <c r="F14" t="n">
-        <v>0.22</v>
+        <v>0.113809589180873</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -766,7 +766,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>0.999586439155041</v>
+        <v>0.999586439155039</v>
       </c>
       <c r="C15" t="n">
         <v>1.46403515763454</v>
@@ -778,10 +778,10 @@
         <v>323.201757881727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0384352417367562</v>
+        <v>0.0384352417367564</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -795,7 +795,7 @@
         <v>2.71575227825572</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0391797972550257</v>
+        <v>0.0391797972550258</v>
       </c>
       <c r="E16" t="n">
         <v>385.787613912786</v>
@@ -804,7 +804,7 @@
         <v>0.171681190023679</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -812,19 +812,19 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>1.11711841032481</v>
+        <v>1.17272365912373</v>
       </c>
       <c r="C17" t="n">
-        <v>3.56612025839991</v>
+        <v>3.50568413101314</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0223423682064962</v>
+        <v>0.0234544731824745</v>
       </c>
       <c r="E17" t="n">
-        <v>428.306012919996</v>
+        <v>425.284206550657</v>
       </c>
       <c r="F17" t="n">
-        <v>0.129465101251646</v>
+        <v>0.129577120210769</v>
       </c>
       <c r="G17" t="s">
         <v>8</v>
@@ -835,19 +835,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.79486274477217</v>
+        <v>1.91110239970552</v>
       </c>
       <c r="C18" t="n">
-        <v>2.50432788985657</v>
+        <v>2.50439321655939</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0358972548954433</v>
+        <v>0.0382220479941103</v>
       </c>
       <c r="E18" t="n">
-        <v>375.216394492828</v>
+        <v>375.219660827969</v>
       </c>
       <c r="F18" t="n">
-        <v>0.129023284057307</v>
+        <v>0.132661336485256</v>
       </c>
       <c r="G18" t="s">
         <v>8</v>
@@ -858,19 +858,19 @@
         <v>26</v>
       </c>
       <c r="B19" t="n">
-        <v>1.88073317781561</v>
+        <v>1.97353195218872</v>
       </c>
       <c r="C19" t="n">
-        <v>3.12509482514695</v>
+        <v>3.08486932368232</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0376146635563123</v>
+        <v>0.0394706390437745</v>
       </c>
       <c r="E19" t="n">
-        <v>406.254741257348</v>
+        <v>404.243466184116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.169442444004338</v>
+        <v>0.169254515107323</v>
       </c>
       <c r="G19" t="s">
         <v>8</v>
@@ -881,22 +881,22 @@
         <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>0.315058689447332</v>
+        <v>0.398592997992733</v>
       </c>
       <c r="C20" t="n">
-        <v>4.4330977883949</v>
+        <v>3.28683105992743</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00630117378894664</v>
+        <v>0.00797185995985466</v>
       </c>
       <c r="E20" t="n">
-        <v>471.654889419745</v>
+        <v>414.341552996372</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0633161106344133</v>
+        <v>0.0457624075101461</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -904,22 +904,22 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>1.22539680568554</v>
+        <v>1.02999814120785</v>
       </c>
       <c r="C21" t="n">
-        <v>3.80487272141349</v>
+        <v>4.19716111388812</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0245079361137108</v>
+        <v>0.020599962824157</v>
       </c>
       <c r="E21" t="n">
-        <v>440.243636070675</v>
+        <v>459.858055694406</v>
       </c>
       <c r="F21" t="n">
-        <v>0.167865500389049</v>
+        <v>0.124353703252758</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -927,22 +927,22 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.25059970266019</v>
+        <v>1.47971422631912</v>
       </c>
       <c r="C22" t="n">
-        <v>3.27043048951258</v>
+        <v>3.07806195353725</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0250119940532037</v>
+        <v>0.0295942845263825</v>
       </c>
       <c r="E22" t="n">
-        <v>413.521524475629</v>
+        <v>403.903097676863</v>
       </c>
       <c r="F22" t="n">
-        <v>0.210710742915288</v>
+        <v>0.165235524113552</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -953,7 +953,7 @@
         <v>3.31313094064339</v>
       </c>
       <c r="C23" t="n">
-        <v>2.5038411019838</v>
+        <v>2.50384110198379</v>
       </c>
       <c r="D23" t="n">
         <v>0.0662626188128678</v>
@@ -965,7 +965,7 @@
         <v>0.171925820258486</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -988,7 +988,7 @@
         <v>0.158065373745723</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -1002,7 +1002,7 @@
         <v>2.33940076682624</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0557829240889023</v>
+        <v>0.0557829240889022</v>
       </c>
       <c r="E25" t="n">
         <v>366.970038341312</v>
@@ -1011,7 +1011,7 @@
         <v>0.167862052302509</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
